--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/BG_NguyenCuong_130826.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 08/01. Báo giá sửa chữa/BG_NguyenCuong_130826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 08\01. Báo giá sửa chữa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10141916-B88F-4CA6-A201-9398AE6C06FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86D5DA9-270F-4A65-AE1C-0BB6BB3DDA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Chờ phản hồi báo giá KD. Lực</t>
+    <t>Khách đã đồng ý sửa, công nợ ghi KD. Lực</t>
   </si>
 </sst>
 </file>
@@ -501,6 +501,78 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -518,78 +590,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1028,26 +1028,26 @@
       <c r="J4" s="58"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="61"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="37"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="15"/>
@@ -1058,11 +1058,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -1072,11 +1072,11 @@
       <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="27" t="s">
@@ -1089,11 +1089,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="27"/>
       <c r="E9" s="27"/>
       <c r="F9" s="27"/>
@@ -1177,17 +1177,17 @@
       <c r="AA11" s="32"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="37"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="61"/>
       <c r="J12" s="22">
         <f>SUM(J11:J11)</f>
         <v>200000</v>
@@ -1222,37 +1222,37 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
       <c r="F15" s="14"/>
-      <c r="G15" s="38" t="s">
+      <c r="G15" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="39" t="s">
+      <c r="G16" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="63"/>
+      <c r="J16" s="63"/>
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
@@ -1310,20 +1310,20 @@
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
       <c r="K21" s="11"/>
       <c r="AA21" s="2"/>
     </row>
@@ -1401,16 +1401,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="17">
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A1:D4"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="E2:J2"/>
-    <mergeCell ref="E3:J3"/>
-    <mergeCell ref="E4:J4"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="G16:J16"/>
@@ -1418,6 +1408,16 @@
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
